--- a/港岛-香港仔及鸭脷洲-扬海/扬海_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-扬海/扬海_销控明细表.xlsx
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>16937100</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>34778</v>
+        <v>34850</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>16937100</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>34778</v>
+        <v>34850</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>130000000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>68349</v>
+        <v>68385</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>130000000</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>68349</v>
+        <v>68385</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>18165600</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>34733</v>
+        <v>34667</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>18165600</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>34733</v>
+        <v>34667</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45531000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>48334</v>
+        <v>48386</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45531000</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>48334</v>
+        <v>48386</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>18057600</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>34527</v>
+        <v>34461</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>18057600</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>34527</v>
+        <v>34461</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>40950000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>43471</v>
+        <v>43518</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>40950000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>43471</v>
+        <v>43518</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>43598400</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>46283</v>
+        <v>46332</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43598400</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>46283</v>
+        <v>46332</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>36510800</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>38759</v>
+        <v>38800</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>36510800</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>38759</v>
+        <v>38800</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>40848640</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>43364</v>
+        <v>43410</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>40848640</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>43364</v>
+        <v>43410</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>17096600</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>32689</v>
+        <v>32627</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>17096600</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>32689</v>
+        <v>32627</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>40854300</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>43370</v>
+        <v>43416</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>40854300</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>43370</v>
+        <v>43416</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>38522400</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>40894</v>
+        <v>40938</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>38522400</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>40894</v>
+        <v>40938</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>16461300</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>31475</v>
+        <v>31415</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>16461300</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>31475</v>
+        <v>31415</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>39052000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>41456</v>
+        <v>41501</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>39052000</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>41456</v>
+        <v>41501</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>15203200</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>32695</v>
+        <v>32766</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>15203200</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>32695</v>
+        <v>32766</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>36948000</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>39223</v>
+        <v>39265</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>36948000</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>39223</v>
+        <v>39265</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>37837000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>40167</v>
+        <v>40209</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>37837000</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>40167</v>
+        <v>40209</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>18883200</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>32060</v>
+        <v>32114</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>18883200</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>32060</v>
+        <v>32114</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>36600000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>38854</v>
+        <v>38895</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>36600000</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>38854</v>
+        <v>38895</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>36521000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>38770</v>
+        <v>38811</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>36521000</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>38770</v>
+        <v>38811</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>15679500</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>33719</v>
+        <v>33792</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>15679500</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>33719</v>
+        <v>33792</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>36266000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>38499</v>
+        <v>38540</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>36266000</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>38499</v>
+        <v>38540</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>15632400</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>33618</v>
+        <v>33691</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>15632400</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>33618</v>
+        <v>33691</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>19590500</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>33261</v>
+        <v>33317</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>19590500</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>33261</v>
+        <v>33317</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>38865200</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>41258</v>
+        <v>41302</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>38865200</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>41258</v>
+        <v>41302</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>38672000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>41053</v>
+        <v>41097</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>38672000</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>41053</v>
+        <v>41097</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>12393700</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>26653</v>
+        <v>26711</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>12393700</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>26653</v>
+        <v>26711</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>35549000</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>37738</v>
+        <v>37778</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>35549000</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>37738</v>
+        <v>37778</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>15491300</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>33315</v>
+        <v>33386</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>15491300</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>33315</v>
+        <v>33386</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>19069100</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>32375</v>
+        <v>32430</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>19069100</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>32375</v>
+        <v>32430</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>14710400</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>31635</v>
+        <v>31703</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>14710400</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>31635</v>
+        <v>31703</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>37318700</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>39616</v>
+        <v>39659</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>37318700</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>39616</v>
+        <v>39659</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>15308200</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>32921</v>
+        <v>32992</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>15308200</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>32921</v>
+        <v>32992</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>36765200</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>39029</v>
+        <v>39070</v>
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>36765200</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>39029</v>
+        <v>39070</v>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>36297600</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>39454</v>
+        <v>39411</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>36297600</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>39454</v>
+        <v>39411</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>36045600</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>39180</v>
+        <v>39137</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>36045600</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>39180</v>
+        <v>39137</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>35795200</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>38908</v>
+        <v>38866</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>35795200</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>38908</v>
+        <v>38866</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         </is>
       </c>
       <c r="E302" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>32520800</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>35349</v>
+        <v>35310</v>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>32520800</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>35349</v>
+        <v>35310</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>29220000</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>31761</v>
+        <v>31726</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>29220000</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>31761</v>
+        <v>31726</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>29915200</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>32517</v>
+        <v>32481</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>29915200</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>32517</v>
+        <v>32481</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>29500800</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>32066</v>
+        <v>32031</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>29500800</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>32066</v>
+        <v>32031</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         </is>
       </c>
       <c r="E374" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>29064000</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>31591</v>
+        <v>31557</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>29064000</v>
       </c>
       <c r="L374" s="5" t="n">
-        <v>31591</v>
+        <v>31557</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         </is>
       </c>
       <c r="E416" s="4" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>28345600</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>30810</v>
+        <v>30777</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>28345600</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>30810</v>
+        <v>30777</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         </is>
       </c>
       <c r="E428" s="4" t="n">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>32503800</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>37232</v>
+        <v>37275</v>
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>32503800</v>
       </c>
       <c r="L428" s="5" t="n">
-        <v>37232</v>
+        <v>37275</v>
       </c>
       <c r="M428" s="3" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         </is>
       </c>
       <c r="E581" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>11575200</v>
       </c>
       <c r="I581" s="5" t="n">
-        <v>34553</v>
+        <v>34656</v>
       </c>
       <c r="J581" s="3" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>11575200</v>
       </c>
       <c r="L581" s="5" t="n">
-        <v>34553</v>
+        <v>34656</v>
       </c>
       <c r="M581" s="3" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         </is>
       </c>
       <c r="E582" s="4" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>14910400</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>31792</v>
+        <v>31724</v>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>14910400</v>
       </c>
       <c r="L582" s="5" t="n">
-        <v>31792</v>
+        <v>31724</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         </is>
       </c>
       <c r="E588" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>9132800</v>
       </c>
       <c r="I588" s="5" t="n">
-        <v>27262</v>
+        <v>27344</v>
       </c>
       <c r="J588" s="3" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>9132800</v>
       </c>
       <c r="L588" s="5" t="n">
-        <v>27262</v>
+        <v>27344</v>
       </c>
       <c r="M588" s="3" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>11102900</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>33143</v>
+        <v>33242</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>11102900</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>33143</v>
+        <v>33242</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         </is>
       </c>
       <c r="E596" s="4" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F596" s="3" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>14777600</v>
       </c>
       <c r="I596" s="5" t="n">
-        <v>31509</v>
+        <v>31442</v>
       </c>
       <c r="J596" s="3" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>14777600</v>
       </c>
       <c r="L596" s="5" t="n">
-        <v>31509</v>
+        <v>31442</v>
       </c>
       <c r="M596" s="3" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         </is>
       </c>
       <c r="E597" s="4" t="n">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F597" s="3" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>16422900</v>
       </c>
       <c r="I597" s="5" t="n">
-        <v>30134</v>
+        <v>30189</v>
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>16422900</v>
       </c>
       <c r="L597" s="5" t="n">
-        <v>30134</v>
+        <v>30189</v>
       </c>
       <c r="M597" s="3" t="inlineStr">
         <is>
@@ -39204,9 +39204,9 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 487呎 (2房)
+          <t>C | 486呎 (2房)
 $1694万
-$34,778/呎
+$34,850/呎
 (22年-02月-15日)</t>
         </is>
       </c>
@@ -39370,15 +39370,15 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 1902呎 (4+房)
+          <t>A | 1901呎 (4+房)
 $13000万
-$68,349/呎
+$68,385/呎
 (24年-06月-18日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>B | 1108呎 (3房)
+          <t>B | 1107呎 (3房)
 -
 -
 (待售)</t>
@@ -39412,9 +39412,9 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $4553万
-$48,334/呎
+$48,386/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -39436,9 +39436,9 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>E | 523呎 (2房)
+          <t>E | 524呎 (2房)
 $1817万
-$34,733/呎
+$34,667/呎
 (21年-09月-30日)</t>
         </is>
       </c>
@@ -39467,9 +39467,9 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $4095万
-$43,471/呎
+$43,518/呎
 (25年-10月-28日)</t>
         </is>
       </c>
@@ -39491,9 +39491,9 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>E | 523呎 (2房)
+          <t>E | 524呎 (2房)
 $1806万
-$34,527/呎
+$34,461/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -39522,9 +39522,9 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $4360万
-$46,283/呎
+$46,332/呎
 (26年-07月-28日)</t>
         </is>
       </c>
@@ -39577,9 +39577,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3651万
-$38,759/呎
+$38,800/呎
 (25年-02月-12日)</t>
         </is>
       </c>
@@ -39632,9 +39632,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $4085万
-$43,364/呎
+$43,410/呎
 (23年-11月-30日)</t>
         </is>
       </c>
@@ -39797,9 +39797,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $4085万
-$43,370/呎
+$43,416/呎
 (21年-10月-07日)</t>
         </is>
       </c>
@@ -39821,9 +39821,9 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 523呎 (2房)
+          <t>E | 524呎 (2房)
 $1710万
-$32,689/呎
+$32,627/呎
 (21年-09月-29日)</t>
         </is>
       </c>
@@ -39852,9 +39852,9 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3852万
-$40,894/呎
+$40,938/呎
 (21年-10月-05日)</t>
         </is>
       </c>
@@ -39907,9 +39907,9 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3905万
-$41,456/呎
+$41,501/呎
 (21年-10月-11日)</t>
         </is>
       </c>
@@ -39931,9 +39931,9 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>E | 523呎 (2房)
+          <t>E | 524呎 (2房)
 $1646万
-$31,475/呎
+$31,415/呎
 (21年-09月-27日)</t>
         </is>
       </c>
@@ -39962,9 +39962,9 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3695万
-$39,223/呎
+$39,265/呎
 (26年-01月-14日)</t>
         </is>
       </c>
@@ -39994,9 +39994,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1520万
-$32,695/呎
+$32,766/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40017,9 +40017,9 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3784万
-$40,167/呎
+$40,209/呎
 (21年-10月-05日)</t>
         </is>
       </c>
@@ -40072,17 +40072,17 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3660万
-$38,854/呎
+$38,895/呎
 (23年-11月-29日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 589呎 (2房)
+          <t>C | 588呎 (2房)
 $1888万
-$32,060/呎
+$32,114/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40127,9 +40127,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3652万
-$38,770/呎
+$38,811/呎
 (24年-04月-25日)</t>
         </is>
       </c>
@@ -40182,9 +40182,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3627万
-$38,499/呎
+$38,540/呎
 (25年-09月-09日)</t>
         </is>
       </c>
@@ -40214,9 +40214,9 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1568万
-$33,719/呎
+$33,792/呎
 (21年-10月-05日)</t>
         </is>
       </c>
@@ -40237,17 +40237,17 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3887万
-$41,258/呎
+$41,302/呎
 (21年-10月-11日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 589呎 (2房)
+          <t>C | 588呎 (2房)
 $1959万
-$33,261/呎
+$33,317/呎
 (21年-10月-08日)</t>
         </is>
       </c>
@@ -40269,9 +40269,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1563万
-$33,618/呎
+$33,691/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40292,9 +40292,9 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3867万
-$41,053/呎
+$41,097/呎
 (21年-10月-12日)</t>
         </is>
       </c>
@@ -40347,9 +40347,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3555万
-$37,738/呎
+$37,778/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -40379,9 +40379,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1239万
-$26,653/呎
+$26,711/呎
 (23年-12月-19日)</t>
         </is>
       </c>
@@ -40410,9 +40410,9 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 589呎 (2房)
+          <t>C | 588呎 (2房)
 $1907万
-$32,375/呎
+$32,430/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40434,9 +40434,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1549万
-$33,315/呎
+$33,386/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40457,9 +40457,9 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3732万
-$39,616/呎
+$39,659/呎
 (21年-09月-18日)</t>
         </is>
       </c>
@@ -40489,9 +40489,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1471万
-$31,635/呎
+$31,703/呎
 (21年-10月-05日)</t>
         </is>
       </c>
@@ -40567,9 +40567,9 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 942呎 (3房)
+          <t>B | 941呎 (3房)
 $3677万
-$39,029/呎
+$39,070/呎
 (21年-10月-15日)</t>
         </is>
       </c>
@@ -40599,9 +40599,9 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 465呎 (2房)
+          <t>F | 464呎 (2房)
 $1531万
-$32,921/呎
+$32,992/呎
 (21年-10月-07日)</t>
         </is>
       </c>
@@ -40862,9 +40862,9 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $3630万
-$39,454/呎
+$39,411/呎
 (21年-10月-06日)</t>
         </is>
       </c>
@@ -40917,9 +40917,9 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $3605万
-$39,180/呎
+$39,137/呎
 (21年-10月-04日)</t>
         </is>
       </c>
@@ -40972,9 +40972,9 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $3580万
-$38,908/呎
+$38,866/呎
 (21年-10月-04日)</t>
         </is>
       </c>
@@ -41192,9 +41192,9 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $3252万
-$35,349/呎
+$35,310/呎
 (21年-09月-27日)</t>
         </is>
       </c>
@@ -41522,9 +41522,9 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $2922万
-$31,761/呎
+$31,726/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -41577,9 +41577,9 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $2992万
-$32,517/呎
+$32,481/呎
 (21年-09月-27日)</t>
         </is>
       </c>
@@ -41687,9 +41687,9 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $2950万
-$32,066/呎
+$32,031/呎
 (21年-09月-30日)</t>
         </is>
       </c>
@@ -41852,9 +41852,9 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $2906万
-$31,591/呎
+$31,557/呎
 (21年-09月-27日)</t>
         </is>
       </c>
@@ -42237,9 +42237,9 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>D | 920呎 (3房)
+          <t>D | 921呎 (3房)
 $2835万
-$30,810/呎
+$30,777/呎
 (21年-10月-05日)</t>
         </is>
       </c>
@@ -42347,9 +42347,9 @@
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>D | 873呎 (3房)
+          <t>D | 872呎 (3房)
 $3250万
-$37,232/呎
+$37,275/呎
 (22年-02月-11日)</t>
         </is>
       </c>
@@ -42542,11 +42542,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -42554,7 +42575,7 @@
 (24年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -42562,8 +42583,8 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -42571,7 +42592,7 @@
 (24年-06月-12日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -42579,7 +42600,7 @@
 (21年-09月-20日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -42588,27 +42609,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -43921,17 +43921,17 @@
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>C | 469呎 (2房)
+          <t>C | 470呎 (2房)
 $1491万
-$31,792/呎
+$31,724/呎
 (21年-09月-30日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>D | 335呎 (1房)
+          <t>D | 334呎 (1房)
 $1158万
-$34,553/呎
+$34,656/呎
 (21年-09月-30日)</t>
         </is>
       </c>
@@ -43992,9 +43992,9 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>D | 335呎 (1房)
+          <t>D | 334呎 (1房)
 $913万
-$27,262/呎
+$27,344/呎
 (24年-04月-15日)</t>
         </is>
       </c>
@@ -44039,25 +44039,25 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>B | 545呎 (2房)
+          <t>B | 544呎 (2房)
 $1642万
-$30,134/呎
+$30,189/呎
 (21年-09月-11日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>C | 469呎 (2房)
+          <t>C | 470呎 (2房)
 $1478万
-$31,509/呎
+$31,442/呎
 (21年-10月-05日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>D | 335呎 (1房)
+          <t>D | 334呎 (1房)
 $1110万
-$33,143/呎
+$33,242/呎
 (21年-09月-11日)</t>
         </is>
       </c>
